--- a/etf_holdings/2026-10-19_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-10-19_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M509"/>
+  <dimension ref="A1:M562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:34</t>
+          <t>2026-10-19 23:51:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:35</t>
+          <t>2026-10-19 23:51:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:36</t>
+          <t>2026-10-19 23:51:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:38</t>
+          <t>2026-10-19 23:51:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:38</t>
+          <t>2026-10-19 23:51:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:38</t>
+          <t>2026-10-19 23:51:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:38</t>
+          <t>2026-10-19 23:51:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:38</t>
+          <t>2026-10-19 23:51:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:38</t>
+          <t>2026-10-19 23:51:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:43</t>
+          <t>2026-10-19 23:51:35</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:44</t>
+          <t>2026-10-19 23:51:36</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:45</t>
+          <t>2026-10-19 23:51:38</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:47</t>
+          <t>2026-10-19 23:51:39</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:47</t>
+          <t>2026-10-19 23:51:39</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:47</t>
+          <t>2026-10-19 23:51:39</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:47</t>
+          <t>2026-10-19 23:51:39</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:47</t>
+          <t>2026-10-19 23:51:39</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:52</t>
+          <t>2026-10-19 23:51:46</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:53</t>
+          <t>2026-10-19 23:51:47</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:55</t>
+          <t>2026-10-19 23:51:48</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:56</t>
+          <t>2026-10-19 23:51:50</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:56</t>
+          <t>2026-10-19 23:51:50</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:56</t>
+          <t>2026-10-19 23:51:50</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:56</t>
+          <t>2026-10-19 23:51:50</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-10-19 23:44:56</t>
+          <t>2026-10-19 23:51:50</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:02</t>
+          <t>2026-10-19 23:51:54</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:03</t>
+          <t>2026-10-19 23:51:56</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:05</t>
+          <t>2026-10-19 23:51:57</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:06</t>
+          <t>2026-10-19 23:51:58</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:12</t>
+          <t>2026-10-19 23:52:02</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:13</t>
+          <t>2026-10-19 23:52:04</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:14</t>
+          <t>2026-10-19 23:52:05</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:16</t>
+          <t>2026-10-19 23:52:06</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:16</t>
+          <t>2026-10-19 23:52:06</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:16</t>
+          <t>2026-10-19 23:52:06</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:16</t>
+          <t>2026-10-19 23:52:06</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:16</t>
+          <t>2026-10-19 23:52:06</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:21</t>
+          <t>2026-10-19 23:52:12</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:22</t>
+          <t>2026-10-19 23:52:13</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:24</t>
+          <t>2026-10-19 23:52:15</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:25</t>
+          <t>2026-10-19 23:52:16</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:25</t>
+          <t>2026-10-19 23:52:16</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:25</t>
+          <t>2026-10-19 23:52:16</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:25</t>
+          <t>2026-10-19 23:52:16</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:25</t>
+          <t>2026-10-19 23:52:16</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:31</t>
+          <t>2026-10-19 23:52:21</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:32</t>
+          <t>2026-10-19 23:52:22</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:33</t>
+          <t>2026-10-19 23:52:23</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:39</t>
+          <t>2026-10-19 23:52:28</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:39</t>
+          <t>2026-10-19 23:52:28</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21873,7 +21873,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:39</t>
+          <t>2026-10-19 23:52:28</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21936,7 +21936,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:40</t>
+          <t>2026-10-19 23:52:29</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:40</t>
+          <t>2026-10-19 23:52:29</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:40</t>
+          <t>2026-10-19 23:52:29</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22125,7 +22125,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:40</t>
+          <t>2026-10-19 23:52:29</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:41</t>
+          <t>2026-10-19 23:52:30</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:47</t>
+          <t>2026-10-19 23:52:35</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:48</t>
+          <t>2026-10-19 23:52:36</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:50</t>
+          <t>2026-10-19 23:52:38</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:56</t>
+          <t>2026-10-19 23:52:46</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:57</t>
+          <t>2026-10-19 23:52:48</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-10-19 23:45:58</t>
+          <t>2026-10-19 23:52:49</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:00</t>
+          <t>2026-10-19 23:52:50</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:00</t>
+          <t>2026-10-19 23:52:50</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:00</t>
+          <t>2026-10-19 23:52:50</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:00</t>
+          <t>2026-10-19 23:52:50</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:00</t>
+          <t>2026-10-19 23:52:50</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:05</t>
+          <t>2026-10-19 23:52:55</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:07</t>
+          <t>2026-10-19 23:52:56</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:09</t>
+          <t>2026-10-19 23:52:57</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:10</t>
+          <t>2026-10-19 23:52:58</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:10</t>
+          <t>2026-10-19 23:52:58</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:10</t>
+          <t>2026-10-19 23:52:58</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:10</t>
+          <t>2026-10-19 23:52:58</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-10-19 23:46:10</t>
+          <t>2026-10-19 23:52:58</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31524,6 +31524,3239 @@
         </is>
       </c>
       <c r="M509" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>1</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>2330台積電</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>0%2420</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>2420</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>8.71%1,094,000</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>8.71%</t>
+        </is>
+      </c>
+      <c r="K510" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>1</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-1.06%4205</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-1.06%</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>4205</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>6.16%445,000</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="K511" t="n">
+        <v>445000</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>1</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>2383台光電</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-0.77%5125</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>5125</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>4.28%254,000</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>4.28%</t>
+        </is>
+      </c>
+      <c r="K512" t="n">
+        <v>254000</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>1</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>1303南亞</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-1.14%303.5</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>303.5</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>4.16%4,167,000</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>4.16%</t>
+        </is>
+      </c>
+      <c r="K513" t="n">
+        <v>4167000</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>1</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>3037欣興</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>+2.75%1120</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>+2.75%</t>
+        </is>
+      </c>
+      <c r="H514" t="n">
+        <v>1120</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>3.94%1,069,000</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>3.94%</t>
+        </is>
+      </c>
+      <c r="K514" t="n">
+        <v>1069000</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>1</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>3017奇鋐</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>+0.15%3320</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="H515" t="n">
+        <v>3320</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>3.59%329,000</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>3.59%</t>
+        </is>
+      </c>
+      <c r="K515" t="n">
+        <v>329000</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>1</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>3653健策</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-2.53%6560</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-2.53%</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>6560</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>3.32%154,000</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="K516" t="n">
+        <v>154000</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>1</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>+0.58%5235</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>5235</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>3.12%181,000</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="K517" t="n">
+        <v>181000</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>1</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>+0.25%2005</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>3.10%470,000</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="K518" t="n">
+        <v>470000</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>1</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>2368金像電</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>+0.4%1250</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>3.02%734,000</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="K519" t="n">
+        <v>734000</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>1</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>2059川湖</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-0.35%9920</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="H520" t="n">
+        <v>9920</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>3.00%92,000</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="K520" t="n">
+        <v>92000</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>1</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>6488環球晶</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-2.22%882</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-2.22%</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>882</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>2.57%884,000</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="K521" t="n">
+        <v>884000</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>1</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>+0.31%1640</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>1640</v>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>2.56%475,000</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="K522" t="n">
+        <v>475000</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>1</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>3443創意</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>+4.68%7830</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>+4.68%</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>7830</v>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>2.50%97,000</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="K523" t="n">
+        <v>97000</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:04</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>1</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>3044健鼎</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-1.2%577</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>577</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>2.44%1,287,000</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>2.44%</t>
+        </is>
+      </c>
+      <c r="K524" t="n">
+        <v>1287000</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>2</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>6505台塑化</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-5.31%116</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-5.31%</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>116</v>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>2.35%6,147,000</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
+      </c>
+      <c r="K525" t="n">
+        <v>6147000</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>2</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>3661世芯-KY</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>+0.81%3715</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>+0.81%</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>3715</v>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>2.25%184,000</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>2.25%</t>
+        </is>
+      </c>
+      <c r="K526" t="n">
+        <v>184000</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>2</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>2303聯電</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-1.13%131.5</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>1.81%4,192,000</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="K527" t="n">
+        <v>4192000</v>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>2</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>6278台表科</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-3.02%289.5</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-3.02%</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>1.74%1,830,000</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="K528" t="n">
+        <v>1830000</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>2</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>2881富邦金</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-1.86%158.5</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>1.62%3,104,000</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="K529" t="n">
+        <v>3104000</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>2</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>2603長榮</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-1.32%262</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-1.32%</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>262</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>1.61%1,871,000</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="K530" t="n">
+        <v>1871000</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>2</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>2891中信金</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-0.27%73.4</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>1.58%6,547,000</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="K531" t="n">
+        <v>6547000</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>2</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-2.42%6245</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-2.42%</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>6245</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>1.56%76,000</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="K532" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>2</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>5274信驊</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-3.03%15980</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-3.03%</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>15980</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>1.49%28,400</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="K533" t="n">
+        <v>28400</v>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>2</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>3036文曄</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-2.14%205.5</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-2.14%</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>1.49%2,208,000</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="K534" t="n">
+        <v>2208000</v>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>2</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>3665貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-1.99%1975</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-1.99%</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>1975</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>1.48%228,000</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="K535" t="n">
+        <v>228000</v>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>2</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>6669緯穎</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>+2.17%1885</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>+2.17%</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>1885</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>1.37%221,000</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="K536" t="n">
+        <v>221000</v>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>2</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>3529力旺</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-2%2695</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>2695</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>1.26%142,000</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="K537" t="n">
+        <v>142000</v>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>2</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>2327國巨*</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-5.82%534</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-5.82%</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>534</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>1.24%708,000</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="K538" t="n">
+        <v>708000</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:05</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>2</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>6187萬潤</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-0.35%1405</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>1405</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>1.15%249,000</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="K539" t="n">
+        <v>249000</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>3</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-0.15%670</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>670</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>1.02%464,000</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="K540" t="n">
+        <v>464000</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>3</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>3231緯創</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-1.37%180</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>180</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>0.96%1,614,000</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="K541" t="n">
+        <v>1614000</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>3</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>3533嘉澤</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>+0.55%1815</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>+0.55%</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>1815</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>0.91%152,000</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="K542" t="n">
+        <v>152000</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>3</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>2313華通</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>0%248</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>248</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>0.90%1,107,336</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="K543" t="n">
+        <v>1107336</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>3</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>6147頎邦</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>+0.24%208</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>208</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>0.88%1,293,000</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="K544" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>3</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>2449京元電子</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-4.18%263.5</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-4.18%</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>0.87%999,000</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="K545" t="n">
+        <v>999000</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>3</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>2317鴻海</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-1.84%239.5</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-1.84%</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>0.76%960,000</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="K546" t="n">
+        <v>960000</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>3</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>7750新代</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-0.55%1820</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>0.73%122,000</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="K547" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>3</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>3081聯亞</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>+0.98%2570</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>+0.98%</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>2570</v>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>0.69%82,000</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="K548" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>3</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>+1.26%2005</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>+1.26%</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>0.69%104,000</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="K549" t="n">
+        <v>104000</v>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>3</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>2637慧洋-KY</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-1.48%100</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-1.48%</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>100</v>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>0.47%1,424,000</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="K550" t="n">
+        <v>1424000</v>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>3</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>4958臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-1.8%547</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>547</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>0.46%257,000</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="K551" t="n">
+        <v>257000</v>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>3</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>5434崇越</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-1.04%570</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>570</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>0.38%200,000</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="K552" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>3</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>3167大量</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-6.26%989</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-6.26%</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>989</v>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>0.37%115,000</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="K553" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:06</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>3</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>3293鈊象</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-2.64%774</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-2.64%</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>774</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>0.34%133,000</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="K554" t="n">
+        <v>133000</v>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>4</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>3090日電貿</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-4.69%162.5</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-4.69%</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>0.32%592,000</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="K555" t="n">
+        <v>592000</v>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>4</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>6271同欣電</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-1.53%225.5</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-1.53%</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>0.25%340,000</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="K556" t="n">
+        <v>340000</v>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>4</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>6121新普</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-1.08%366</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-1.08%</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>366</v>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>0.21%178,000</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K557" t="n">
+        <v>178000</v>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>4</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>3374精材</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>+1.04%438</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>+1.04%</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>438</v>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>0.14%100,000</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="K558" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>4</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>7769鴻勁</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>+2.18%5400</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>+2.18%</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>0.12%7,000</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="K559" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>4</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>9939宏全</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-1.95%125.5</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-1.95%</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>0.07%180,000</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="K560" t="n">
+        <v>180000</v>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>4</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>1476儒鴻</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-2.58%321</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-2.58%</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>321</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>0.07%70,000</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="K561" t="n">
+        <v>70000</v>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>4</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>1215卜蜂</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-0.47%106.5</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>0.07%200,000</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="K562" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
